--- a/exports/NursIT_Allgemeine_Verbandsklassen.xlsx
+++ b/exports/NursIT_Allgemeine_Verbandsklassen.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mertakdemir/Developer/uni/Modell/exports/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2142C364-ED42-A34F-B53C-C8161897DB17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8326259D-6808-444E-9BC1-D97190F667FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="28200" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="35060" windowHeight="27800" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NursIT Experte" sheetId="2" r:id="rId1"/>
@@ -4239,21 +4239,25 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF0F172A"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="8">
@@ -14890,6 +14894,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -26922,6 +26927,18 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A63:A65"/>
+    <mergeCell ref="A15:A17"/>
+    <mergeCell ref="A24:A26"/>
+    <mergeCell ref="A48:A50"/>
+    <mergeCell ref="A51:A53"/>
+    <mergeCell ref="A60:A62"/>
+    <mergeCell ref="A54:A56"/>
+    <mergeCell ref="A45:A47"/>
+    <mergeCell ref="A21:A23"/>
+    <mergeCell ref="A12:A14"/>
+    <mergeCell ref="A57:A59"/>
+    <mergeCell ref="A33:A35"/>
     <mergeCell ref="A6:A8"/>
     <mergeCell ref="A3:A5"/>
     <mergeCell ref="A42:A44"/>
@@ -26931,20 +26948,9 @@
     <mergeCell ref="A36:A38"/>
     <mergeCell ref="A30:A32"/>
     <mergeCell ref="A39:A41"/>
-    <mergeCell ref="A45:A47"/>
-    <mergeCell ref="A21:A23"/>
-    <mergeCell ref="A12:A14"/>
-    <mergeCell ref="A57:A59"/>
-    <mergeCell ref="A33:A35"/>
-    <mergeCell ref="A63:A65"/>
-    <mergeCell ref="A15:A17"/>
-    <mergeCell ref="A24:A26"/>
-    <mergeCell ref="A48:A50"/>
-    <mergeCell ref="A51:A53"/>
-    <mergeCell ref="A60:A62"/>
-    <mergeCell ref="A54:A56"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -26954,7 +26960,7 @@
   <dimension ref="A1:BJ86"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="62" width="36" customWidth="1"/>
   </cols>
@@ -42883,12 +42889,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A83:A86"/>
-    <mergeCell ref="A39:A42"/>
-    <mergeCell ref="A15:A18"/>
-    <mergeCell ref="A59:A62"/>
-    <mergeCell ref="A35:A38"/>
-    <mergeCell ref="A51:A54"/>
     <mergeCell ref="A3:A6"/>
     <mergeCell ref="A55:A58"/>
     <mergeCell ref="A71:A74"/>
@@ -42900,12 +42900,19 @@
     <mergeCell ref="A31:A34"/>
     <mergeCell ref="A43:A46"/>
     <mergeCell ref="A67:A70"/>
+    <mergeCell ref="A11:A14"/>
+    <mergeCell ref="A7:A10"/>
+    <mergeCell ref="A83:A86"/>
+    <mergeCell ref="A39:A42"/>
+    <mergeCell ref="A15:A18"/>
+    <mergeCell ref="A59:A62"/>
+    <mergeCell ref="A35:A38"/>
+    <mergeCell ref="A51:A54"/>
     <mergeCell ref="A79:A82"/>
-    <mergeCell ref="A11:A14"/>
     <mergeCell ref="A75:A78"/>
-    <mergeCell ref="A7:A10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/exports/NursIT_Allgemeine_Verbandsklassen.xlsx
+++ b/exports/NursIT_Allgemeine_Verbandsklassen.xlsx
@@ -8,16 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mertakdemir/Developer/uni/Modell/exports/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8326259D-6808-444E-9BC1-D97190F667FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{140EC29A-4F56-8445-B299-CCF6D863FCD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="35060" windowHeight="27800" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="28200" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NursIT Experte" sheetId="2" r:id="rId1"/>
     <sheet name="KI-Antworten" sheetId="3" r:id="rId2"/>
     <sheet name="Alle im Vergleich" sheetId="1" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Alle im Vergleich'!$A:$B,'Alle im Vergleich'!$1:$1</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -4226,7 +4242,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -10681,14 +10697,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:BJ23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="62" width="36" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:62" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:62" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -10876,7 +10892,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:62" ht="140" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:62" ht="140" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>62</v>
       </c>
@@ -10944,7 +10960,7 @@
       <c r="BI2" s="4"/>
       <c r="BJ2" s="4"/>
     </row>
-    <row r="3" spans="1:62" ht="45" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:62" ht="45">
       <c r="A3" s="13" t="s">
         <v>64</v>
       </c>
@@ -11132,7 +11148,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="4" spans="1:62" ht="165" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:62" ht="165">
       <c r="A4" s="13" t="s">
         <v>217</v>
       </c>
@@ -11320,7 +11336,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="5" spans="1:62" ht="75" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:62" ht="75">
       <c r="A5" s="13" t="s">
         <v>312</v>
       </c>
@@ -11508,7 +11524,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="6" spans="1:62" ht="30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:62" ht="30">
       <c r="A6" s="13" t="s">
         <v>518</v>
       </c>
@@ -11696,7 +11712,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="7" spans="1:62" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:62" ht="16">
       <c r="A7" s="13" t="s">
         <v>552</v>
       </c>
@@ -11884,7 +11900,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="8" spans="1:62" ht="16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:62" ht="16">
       <c r="A8" s="13" t="s">
         <v>557</v>
       </c>
@@ -12072,7 +12088,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="9" spans="1:62" ht="30" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:62" ht="30">
       <c r="A9" s="13" t="s">
         <v>561</v>
       </c>
@@ -12260,7 +12276,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="10" spans="1:62" ht="16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:62" ht="16">
       <c r="A10" s="13" t="s">
         <v>568</v>
       </c>
@@ -12448,7 +12464,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="11" spans="1:62" ht="30" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:62" ht="30">
       <c r="A11" s="13" t="s">
         <v>573</v>
       </c>
@@ -12636,7 +12652,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="12" spans="1:62" ht="60" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:62" ht="60">
       <c r="A12" s="13" t="s">
         <v>618</v>
       </c>
@@ -12824,7 +12840,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="13" spans="1:62" ht="210" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:62" ht="210">
       <c r="A13" s="13" t="s">
         <v>671</v>
       </c>
@@ -13012,7 +13028,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="14" spans="1:62" ht="16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:62" ht="16">
       <c r="A14" s="13" t="s">
         <v>868</v>
       </c>
@@ -13200,7 +13216,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="15" spans="1:62" ht="75" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:62" ht="75">
       <c r="A15" s="13" t="s">
         <v>869</v>
       </c>
@@ -13388,7 +13404,7 @@
         <v>875</v>
       </c>
     </row>
-    <row r="16" spans="1:62" ht="60" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:62" ht="60">
       <c r="A16" s="13" t="s">
         <v>923</v>
       </c>
@@ -13576,7 +13592,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="17" spans="1:62" ht="60" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:62" ht="60">
       <c r="A17" s="13" t="s">
         <v>938</v>
       </c>
@@ -13764,7 +13780,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="18" spans="1:62" ht="60" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:62" ht="60">
       <c r="A18" s="13" t="s">
         <v>980</v>
       </c>
@@ -13952,7 +13968,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="19" spans="1:62" ht="45" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:62" ht="45">
       <c r="A19" s="13" t="s">
         <v>1017</v>
       </c>
@@ -14140,7 +14156,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="20" spans="1:62" ht="45" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:62" ht="45">
       <c r="A20" s="13" t="s">
         <v>1079</v>
       </c>
@@ -14328,7 +14344,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="21" spans="1:62" ht="16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:62" ht="16">
       <c r="A21" s="13" t="s">
         <v>1097</v>
       </c>
@@ -14516,7 +14532,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="22" spans="1:62" ht="45" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:62" ht="45">
       <c r="A22" s="13" t="s">
         <v>1099</v>
       </c>
@@ -14704,7 +14720,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="23" spans="1:62" ht="135" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:62" ht="135">
       <c r="A23" s="13" t="s">
         <v>1108</v>
       </c>
@@ -14902,14 +14918,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:BJ65"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="62" width="36" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:62" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:62" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -15097,7 +15113,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:62" ht="140" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:62" ht="140" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>62</v>
       </c>
@@ -15165,7 +15181,7 @@
       <c r="BI2" s="4"/>
       <c r="BJ2" s="4"/>
     </row>
-    <row r="3" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:62">
       <c r="A3" s="19" t="s">
         <v>64</v>
       </c>
@@ -15353,7 +15369,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="4" spans="1:62" ht="45" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:62" ht="45">
       <c r="A4" s="17"/>
       <c r="B4" s="9" t="s">
         <v>111</v>
@@ -15539,7 +15555,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="5" spans="1:62" ht="30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:62" ht="30">
       <c r="A5" s="18"/>
       <c r="B5" s="11" t="s">
         <v>170</v>
@@ -15725,7 +15741,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="6" spans="1:62" ht="30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:62" ht="30">
       <c r="A6" s="19" t="s">
         <v>217</v>
       </c>
@@ -15913,7 +15929,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="7" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:62">
       <c r="A7" s="17"/>
       <c r="B7" s="9" t="s">
         <v>111</v>
@@ -16099,7 +16115,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="8" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:62">
       <c r="A8" s="18"/>
       <c r="B8" s="11" t="s">
         <v>170</v>
@@ -16285,7 +16301,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="9" spans="1:62" ht="30" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:62" ht="30">
       <c r="A9" s="19" t="s">
         <v>312</v>
       </c>
@@ -16473,7 +16489,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="10" spans="1:62" ht="30" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:62" ht="30">
       <c r="A10" s="17"/>
       <c r="B10" s="9" t="s">
         <v>111</v>
@@ -16659,7 +16675,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="11" spans="1:62" ht="60" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:62" ht="60">
       <c r="A11" s="18"/>
       <c r="B11" s="11" t="s">
         <v>170</v>
@@ -16845,7 +16861,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="12" spans="1:62" ht="30" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:62" ht="30">
       <c r="A12" s="19" t="s">
         <v>518</v>
       </c>
@@ -17033,7 +17049,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="13" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:62">
       <c r="A13" s="17"/>
       <c r="B13" s="9" t="s">
         <v>111</v>
@@ -17219,7 +17235,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="14" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:62">
       <c r="A14" s="18"/>
       <c r="B14" s="11" t="s">
         <v>170</v>
@@ -17405,7 +17421,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="15" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:62">
       <c r="A15" s="19" t="s">
         <v>552</v>
       </c>
@@ -17593,7 +17609,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="16" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:62">
       <c r="A16" s="17"/>
       <c r="B16" s="9" t="s">
         <v>111</v>
@@ -17779,7 +17795,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="17" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:62">
       <c r="A17" s="18"/>
       <c r="B17" s="11" t="s">
         <v>170</v>
@@ -17965,7 +17981,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="18" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:62">
       <c r="A18" s="19" t="s">
         <v>557</v>
       </c>
@@ -18153,7 +18169,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="19" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:62">
       <c r="A19" s="17"/>
       <c r="B19" s="9" t="s">
         <v>111</v>
@@ -18339,7 +18355,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="20" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:62">
       <c r="A20" s="18"/>
       <c r="B20" s="11" t="s">
         <v>170</v>
@@ -18525,7 +18541,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="21" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:62">
       <c r="A21" s="19" t="s">
         <v>561</v>
       </c>
@@ -18713,7 +18729,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="22" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:62">
       <c r="A22" s="17"/>
       <c r="B22" s="9" t="s">
         <v>111</v>
@@ -18899,7 +18915,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="23" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:62">
       <c r="A23" s="18"/>
       <c r="B23" s="11" t="s">
         <v>170</v>
@@ -19085,7 +19101,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="24" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:62">
       <c r="A24" s="19" t="s">
         <v>568</v>
       </c>
@@ -19273,7 +19289,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="25" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:62">
       <c r="A25" s="17"/>
       <c r="B25" s="9" t="s">
         <v>111</v>
@@ -19459,7 +19475,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="26" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:62">
       <c r="A26" s="18"/>
       <c r="B26" s="11" t="s">
         <v>170</v>
@@ -19645,7 +19661,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="27" spans="1:62" ht="30" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:62" ht="30">
       <c r="A27" s="19" t="s">
         <v>573</v>
       </c>
@@ -19833,7 +19849,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="28" spans="1:62" ht="30" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:62" ht="30">
       <c r="A28" s="17"/>
       <c r="B28" s="9" t="s">
         <v>111</v>
@@ -20019,7 +20035,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="29" spans="1:62" ht="30" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:62" ht="30">
       <c r="A29" s="18"/>
       <c r="B29" s="11" t="s">
         <v>170</v>
@@ -20205,7 +20221,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="30" spans="1:62" ht="60" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:62" ht="60">
       <c r="A30" s="19" t="s">
         <v>618</v>
       </c>
@@ -20393,7 +20409,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="31" spans="1:62" ht="45" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:62" ht="45">
       <c r="A31" s="17"/>
       <c r="B31" s="9" t="s">
         <v>111</v>
@@ -20579,7 +20595,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="32" spans="1:62" ht="60" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:62" ht="60">
       <c r="A32" s="18"/>
       <c r="B32" s="11" t="s">
         <v>170</v>
@@ -20765,7 +20781,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="33" spans="1:62" ht="60" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:62" ht="60">
       <c r="A33" s="19" t="s">
         <v>671</v>
       </c>
@@ -20953,7 +20969,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="34" spans="1:62" ht="60" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:62" ht="60">
       <c r="A34" s="17"/>
       <c r="B34" s="9" t="s">
         <v>111</v>
@@ -21139,7 +21155,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="35" spans="1:62" ht="75" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:62" ht="75">
       <c r="A35" s="18"/>
       <c r="B35" s="11" t="s">
         <v>170</v>
@@ -21325,7 +21341,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="36" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:62">
       <c r="A36" s="19" t="s">
         <v>868</v>
       </c>
@@ -21513,7 +21529,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="37" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:62">
       <c r="A37" s="17"/>
       <c r="B37" s="9" t="s">
         <v>111</v>
@@ -21699,7 +21715,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="38" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:62">
       <c r="A38" s="18"/>
       <c r="B38" s="11" t="s">
         <v>170</v>
@@ -21885,7 +21901,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="39" spans="1:62" ht="60" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:62" ht="60">
       <c r="A39" s="19" t="s">
         <v>869</v>
       </c>
@@ -22073,7 +22089,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="40" spans="1:62" ht="30" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:62" ht="30">
       <c r="A40" s="17"/>
       <c r="B40" s="9" t="s">
         <v>111</v>
@@ -22259,7 +22275,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="41" spans="1:62" ht="45" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:62" ht="45">
       <c r="A41" s="18"/>
       <c r="B41" s="11" t="s">
         <v>170</v>
@@ -22445,7 +22461,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="42" spans="1:62" ht="30" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:62" ht="30">
       <c r="A42" s="19" t="s">
         <v>923</v>
       </c>
@@ -22633,7 +22649,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="43" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:62">
       <c r="A43" s="17"/>
       <c r="B43" s="9" t="s">
         <v>111</v>
@@ -22819,7 +22835,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="44" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:62">
       <c r="A44" s="18"/>
       <c r="B44" s="11" t="s">
         <v>170</v>
@@ -23005,7 +23021,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="45" spans="1:62" ht="30" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:62" ht="30">
       <c r="A45" s="19" t="s">
         <v>938</v>
       </c>
@@ -23193,7 +23209,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="46" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:62">
       <c r="A46" s="17"/>
       <c r="B46" s="9" t="s">
         <v>111</v>
@@ -23379,7 +23395,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="47" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:62">
       <c r="A47" s="18"/>
       <c r="B47" s="11" t="s">
         <v>170</v>
@@ -23565,7 +23581,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="48" spans="1:62" ht="30" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:62" ht="30">
       <c r="A48" s="19" t="s">
         <v>980</v>
       </c>
@@ -23753,7 +23769,7 @@
         <v>1012</v>
       </c>
     </row>
-    <row r="49" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:62">
       <c r="A49" s="17"/>
       <c r="B49" s="9" t="s">
         <v>111</v>
@@ -23939,7 +23955,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="50" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:62">
       <c r="A50" s="18"/>
       <c r="B50" s="11" t="s">
         <v>170</v>
@@ -24125,7 +24141,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="51" spans="1:62" ht="30" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:62" ht="30">
       <c r="A51" s="19" t="s">
         <v>1017</v>
       </c>
@@ -24313,7 +24329,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="52" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:62">
       <c r="A52" s="17"/>
       <c r="B52" s="9" t="s">
         <v>111</v>
@@ -24499,7 +24515,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="53" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:62">
       <c r="A53" s="18"/>
       <c r="B53" s="11" t="s">
         <v>170</v>
@@ -24685,7 +24701,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="54" spans="1:62" ht="30" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:62" ht="30">
       <c r="A54" s="19" t="s">
         <v>1079</v>
       </c>
@@ -24873,7 +24889,7 @@
         <v>1095</v>
       </c>
     </row>
-    <row r="55" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:62">
       <c r="A55" s="17"/>
       <c r="B55" s="9" t="s">
         <v>111</v>
@@ -25059,7 +25075,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="56" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:62">
       <c r="A56" s="18"/>
       <c r="B56" s="11" t="s">
         <v>170</v>
@@ -25245,7 +25261,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="57" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:62">
       <c r="A57" s="19" t="s">
         <v>1097</v>
       </c>
@@ -25433,7 +25449,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="58" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:62">
       <c r="A58" s="17"/>
       <c r="B58" s="9" t="s">
         <v>111</v>
@@ -25619,7 +25635,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="59" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:62">
       <c r="A59" s="18"/>
       <c r="B59" s="11" t="s">
         <v>170</v>
@@ -25805,7 +25821,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="60" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:62">
       <c r="A60" s="19" t="s">
         <v>1099</v>
       </c>
@@ -25993,7 +26009,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="61" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:62">
       <c r="A61" s="17"/>
       <c r="B61" s="9" t="s">
         <v>111</v>
@@ -26179,7 +26195,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="62" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:62">
       <c r="A62" s="18"/>
       <c r="B62" s="11" t="s">
         <v>170</v>
@@ -26365,7 +26381,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="63" spans="1:62" ht="120" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:62" ht="120">
       <c r="A63" s="19" t="s">
         <v>1108</v>
       </c>
@@ -26553,7 +26569,7 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="64" spans="1:62" ht="120" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:62" ht="120">
       <c r="A64" s="17"/>
       <c r="B64" s="9" t="s">
         <v>111</v>
@@ -26739,7 +26755,7 @@
         <v>1257</v>
       </c>
     </row>
-    <row r="65" spans="1:62" ht="195" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:62" ht="195">
       <c r="A65" s="18"/>
       <c r="B65" s="11" t="s">
         <v>170</v>
@@ -26927,15 +26943,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A63:A65"/>
-    <mergeCell ref="A15:A17"/>
-    <mergeCell ref="A24:A26"/>
-    <mergeCell ref="A48:A50"/>
-    <mergeCell ref="A51:A53"/>
-    <mergeCell ref="A60:A62"/>
-    <mergeCell ref="A54:A56"/>
-    <mergeCell ref="A45:A47"/>
-    <mergeCell ref="A21:A23"/>
     <mergeCell ref="A12:A14"/>
     <mergeCell ref="A57:A59"/>
     <mergeCell ref="A33:A35"/>
@@ -26948,6 +26955,15 @@
     <mergeCell ref="A36:A38"/>
     <mergeCell ref="A30:A32"/>
     <mergeCell ref="A39:A41"/>
+    <mergeCell ref="A63:A65"/>
+    <mergeCell ref="A15:A17"/>
+    <mergeCell ref="A24:A26"/>
+    <mergeCell ref="A48:A50"/>
+    <mergeCell ref="A51:A53"/>
+    <mergeCell ref="A60:A62"/>
+    <mergeCell ref="A54:A56"/>
+    <mergeCell ref="A45:A47"/>
+    <mergeCell ref="A21:A23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -26957,15 +26973,21 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:BJ86"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="62" width="36" customWidth="1"/>
+    <col min="3" max="3" width="33.33203125" customWidth="1"/>
+    <col min="4" max="4" width="30.5" customWidth="1"/>
+    <col min="5" max="5" width="29.83203125" customWidth="1"/>
+    <col min="6" max="62" width="36" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:62" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:62" ht="25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -27153,7 +27175,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:62" ht="140" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:62" ht="140" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>62</v>
       </c>
@@ -27221,7 +27243,7 @@
       <c r="BI2" s="4"/>
       <c r="BJ2" s="4"/>
     </row>
-    <row r="3" spans="1:62" ht="45" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:62" ht="45">
       <c r="A3" s="16" t="s">
         <v>64</v>
       </c>
@@ -27409,7 +27431,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="4" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:62">
       <c r="A4" s="17"/>
       <c r="B4" s="7" t="s">
         <v>102</v>
@@ -27595,7 +27617,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="5" spans="1:62" ht="45" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:62" ht="45">
       <c r="A5" s="17"/>
       <c r="B5" s="9" t="s">
         <v>111</v>
@@ -27781,7 +27803,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="6" spans="1:62" ht="30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:62" ht="30">
       <c r="A6" s="18"/>
       <c r="B6" s="11" t="s">
         <v>170</v>
@@ -27967,7 +27989,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="7" spans="1:62" ht="165" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:62" ht="97" customHeight="1">
       <c r="A7" s="16" t="s">
         <v>217</v>
       </c>
@@ -28155,7 +28177,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="8" spans="1:62" ht="30" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:62" ht="30">
       <c r="A8" s="17"/>
       <c r="B8" s="7" t="s">
         <v>102</v>
@@ -28341,7 +28363,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="9" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:62">
       <c r="A9" s="17"/>
       <c r="B9" s="9" t="s">
         <v>111</v>
@@ -28527,7 +28549,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="10" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:62">
       <c r="A10" s="18"/>
       <c r="B10" s="11" t="s">
         <v>170</v>
@@ -28713,7 +28735,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="11" spans="1:62" ht="75" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:62" ht="75">
       <c r="A11" s="16" t="s">
         <v>312</v>
       </c>
@@ -28901,7 +28923,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="12" spans="1:62" ht="30" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:62" ht="30">
       <c r="A12" s="17"/>
       <c r="B12" s="7" t="s">
         <v>102</v>
@@ -29087,7 +29109,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="13" spans="1:62" ht="30" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:62" ht="30">
       <c r="A13" s="17"/>
       <c r="B13" s="9" t="s">
         <v>111</v>
@@ -29273,7 +29295,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="14" spans="1:62" ht="60" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:62" ht="60">
       <c r="A14" s="18"/>
       <c r="B14" s="11" t="s">
         <v>170</v>
@@ -29459,7 +29481,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="15" spans="1:62" ht="30" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:62" ht="30">
       <c r="A15" s="16" t="s">
         <v>518</v>
       </c>
@@ -29647,7 +29669,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="16" spans="1:62" ht="30" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:62" ht="30">
       <c r="A16" s="17"/>
       <c r="B16" s="7" t="s">
         <v>102</v>
@@ -29833,7 +29855,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="17" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:62">
       <c r="A17" s="17"/>
       <c r="B17" s="9" t="s">
         <v>111</v>
@@ -30019,7 +30041,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="18" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:62">
       <c r="A18" s="18"/>
       <c r="B18" s="11" t="s">
         <v>170</v>
@@ -30205,7 +30227,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="19" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:62">
       <c r="A19" s="16" t="s">
         <v>552</v>
       </c>
@@ -30393,7 +30415,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="20" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:62">
       <c r="A20" s="17"/>
       <c r="B20" s="7" t="s">
         <v>102</v>
@@ -30579,7 +30601,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="21" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:62">
       <c r="A21" s="17"/>
       <c r="B21" s="9" t="s">
         <v>111</v>
@@ -30765,7 +30787,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="22" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:62">
       <c r="A22" s="18"/>
       <c r="B22" s="11" t="s">
         <v>170</v>
@@ -30951,7 +30973,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="23" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:62" ht="30">
       <c r="A23" s="16" t="s">
         <v>557</v>
       </c>
@@ -31139,7 +31161,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="24" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:62" ht="30">
       <c r="A24" s="17"/>
       <c r="B24" s="7" t="s">
         <v>102</v>
@@ -31325,7 +31347,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="25" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:62">
       <c r="A25" s="17"/>
       <c r="B25" s="9" t="s">
         <v>111</v>
@@ -31511,7 +31533,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="26" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:62">
       <c r="A26" s="18"/>
       <c r="B26" s="11" t="s">
         <v>170</v>
@@ -31697,7 +31719,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="27" spans="1:62" ht="30" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:62" ht="30">
       <c r="A27" s="16" t="s">
         <v>561</v>
       </c>
@@ -31885,7 +31907,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="28" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:62">
       <c r="A28" s="17"/>
       <c r="B28" s="7" t="s">
         <v>102</v>
@@ -32071,7 +32093,7 @@
         <v>567</v>
       </c>
     </row>
-    <row r="29" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:62">
       <c r="A29" s="17"/>
       <c r="B29" s="9" t="s">
         <v>111</v>
@@ -32257,7 +32279,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="30" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:62">
       <c r="A30" s="18"/>
       <c r="B30" s="11" t="s">
         <v>170</v>
@@ -32443,7 +32465,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="31" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:62">
       <c r="A31" s="16" t="s">
         <v>568</v>
       </c>
@@ -32631,7 +32653,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="32" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:62">
       <c r="A32" s="17"/>
       <c r="B32" s="7" t="s">
         <v>102</v>
@@ -32817,7 +32839,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="33" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:62">
       <c r="A33" s="17"/>
       <c r="B33" s="9" t="s">
         <v>111</v>
@@ -33003,7 +33025,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="34" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:62">
       <c r="A34" s="18"/>
       <c r="B34" s="11" t="s">
         <v>170</v>
@@ -33189,7 +33211,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="35" spans="1:62" ht="30" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:62" ht="30">
       <c r="A35" s="16" t="s">
         <v>573</v>
       </c>
@@ -33377,7 +33399,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="36" spans="1:62" ht="30" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:62" ht="30">
       <c r="A36" s="17"/>
       <c r="B36" s="7" t="s">
         <v>102</v>
@@ -33563,7 +33585,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="37" spans="1:62" ht="30" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:62" ht="30">
       <c r="A37" s="17"/>
       <c r="B37" s="9" t="s">
         <v>111</v>
@@ -33749,7 +33771,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="38" spans="1:62" ht="30" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:62" ht="30">
       <c r="A38" s="18"/>
       <c r="B38" s="11" t="s">
         <v>170</v>
@@ -33935,7 +33957,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="39" spans="1:62" ht="60" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:62" ht="60">
       <c r="A39" s="16" t="s">
         <v>618</v>
       </c>
@@ -34123,7 +34145,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="40" spans="1:62" ht="60" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:62" ht="60">
       <c r="A40" s="17"/>
       <c r="B40" s="7" t="s">
         <v>102</v>
@@ -34309,7 +34331,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="41" spans="1:62" ht="45" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:62" ht="45">
       <c r="A41" s="17"/>
       <c r="B41" s="9" t="s">
         <v>111</v>
@@ -34495,7 +34517,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="42" spans="1:62" ht="60" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:62" ht="60">
       <c r="A42" s="18"/>
       <c r="B42" s="11" t="s">
         <v>170</v>
@@ -34681,7 +34703,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="43" spans="1:62" ht="210" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:62" ht="210">
       <c r="A43" s="16" t="s">
         <v>671</v>
       </c>
@@ -34869,7 +34891,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="44" spans="1:62" ht="60" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:62" ht="60">
       <c r="A44" s="17"/>
       <c r="B44" s="7" t="s">
         <v>102</v>
@@ -35055,7 +35077,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="45" spans="1:62" ht="60" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:62" ht="60">
       <c r="A45" s="17"/>
       <c r="B45" s="9" t="s">
         <v>111</v>
@@ -35241,7 +35263,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="46" spans="1:62" ht="75" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:62" ht="90">
       <c r="A46" s="18"/>
       <c r="B46" s="11" t="s">
         <v>170</v>
@@ -35427,7 +35449,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="47" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:62">
       <c r="A47" s="16" t="s">
         <v>868</v>
       </c>
@@ -35615,7 +35637,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="48" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:62">
       <c r="A48" s="17"/>
       <c r="B48" s="7" t="s">
         <v>102</v>
@@ -35801,7 +35823,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="49" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:62">
       <c r="A49" s="17"/>
       <c r="B49" s="9" t="s">
         <v>111</v>
@@ -35987,7 +36009,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="50" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:62">
       <c r="A50" s="18"/>
       <c r="B50" s="11" t="s">
         <v>170</v>
@@ -36173,7 +36195,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="51" spans="1:62" ht="75" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:62" ht="75">
       <c r="A51" s="16" t="s">
         <v>869</v>
       </c>
@@ -36361,7 +36383,7 @@
         <v>875</v>
       </c>
     </row>
-    <row r="52" spans="1:62" ht="60" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:62" ht="60">
       <c r="A52" s="17"/>
       <c r="B52" s="7" t="s">
         <v>102</v>
@@ -36547,7 +36569,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="53" spans="1:62" ht="30" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:62" ht="30">
       <c r="A53" s="17"/>
       <c r="B53" s="9" t="s">
         <v>111</v>
@@ -36733,7 +36755,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="54" spans="1:62" ht="45" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:62" ht="45">
       <c r="A54" s="18"/>
       <c r="B54" s="11" t="s">
         <v>170</v>
@@ -36919,7 +36941,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="55" spans="1:62" ht="60" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:62" ht="60">
       <c r="A55" s="16" t="s">
         <v>923</v>
       </c>
@@ -37107,7 +37129,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="56" spans="1:62" ht="30" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:62" ht="30">
       <c r="A56" s="17"/>
       <c r="B56" s="7" t="s">
         <v>102</v>
@@ -37293,7 +37315,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="57" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:62">
       <c r="A57" s="17"/>
       <c r="B57" s="9" t="s">
         <v>111</v>
@@ -37479,7 +37501,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="58" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:62">
       <c r="A58" s="18"/>
       <c r="B58" s="11" t="s">
         <v>170</v>
@@ -37665,7 +37687,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="59" spans="1:62" ht="60" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:62" ht="60">
       <c r="A59" s="16" t="s">
         <v>938</v>
       </c>
@@ -37853,7 +37875,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="60" spans="1:62" ht="30" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:62" ht="45">
       <c r="A60" s="17"/>
       <c r="B60" s="7" t="s">
         <v>102</v>
@@ -38039,7 +38061,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="61" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:62">
       <c r="A61" s="17"/>
       <c r="B61" s="9" t="s">
         <v>111</v>
@@ -38225,7 +38247,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="62" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:62">
       <c r="A62" s="18"/>
       <c r="B62" s="11" t="s">
         <v>170</v>
@@ -38411,7 +38433,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="63" spans="1:62" ht="60" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:62" ht="60">
       <c r="A63" s="16" t="s">
         <v>980</v>
       </c>
@@ -38599,7 +38621,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="64" spans="1:62" ht="30" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:62" ht="30">
       <c r="A64" s="17"/>
       <c r="B64" s="7" t="s">
         <v>102</v>
@@ -38785,7 +38807,7 @@
         <v>1012</v>
       </c>
     </row>
-    <row r="65" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:62">
       <c r="A65" s="17"/>
       <c r="B65" s="9" t="s">
         <v>111</v>
@@ -38971,7 +38993,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="66" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:62">
       <c r="A66" s="18"/>
       <c r="B66" s="11" t="s">
         <v>170</v>
@@ -39157,7 +39179,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="67" spans="1:62" ht="45" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:62" ht="45">
       <c r="A67" s="16" t="s">
         <v>1017</v>
       </c>
@@ -39345,7 +39367,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="68" spans="1:62" ht="30" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:62" ht="30">
       <c r="A68" s="17"/>
       <c r="B68" s="7" t="s">
         <v>102</v>
@@ -39531,7 +39553,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="69" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:62">
       <c r="A69" s="17"/>
       <c r="B69" s="9" t="s">
         <v>111</v>
@@ -39717,7 +39739,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="70" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:62">
       <c r="A70" s="18"/>
       <c r="B70" s="11" t="s">
         <v>170</v>
@@ -39903,7 +39925,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="71" spans="1:62" ht="45" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:62" ht="45">
       <c r="A71" s="16" t="s">
         <v>1079</v>
       </c>
@@ -40091,7 +40113,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="72" spans="1:62" ht="30" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:62" ht="30">
       <c r="A72" s="17"/>
       <c r="B72" s="7" t="s">
         <v>102</v>
@@ -40277,7 +40299,7 @@
         <v>1095</v>
       </c>
     </row>
-    <row r="73" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:62">
       <c r="A73" s="17"/>
       <c r="B73" s="9" t="s">
         <v>111</v>
@@ -40463,7 +40485,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="74" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:62">
       <c r="A74" s="18"/>
       <c r="B74" s="11" t="s">
         <v>170</v>
@@ -40649,7 +40671,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="75" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:62">
       <c r="A75" s="16" t="s">
         <v>1097</v>
       </c>
@@ -40837,7 +40859,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="76" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:62">
       <c r="A76" s="17"/>
       <c r="B76" s="7" t="s">
         <v>102</v>
@@ -41023,7 +41045,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="77" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:62">
       <c r="A77" s="17"/>
       <c r="B77" s="9" t="s">
         <v>111</v>
@@ -41209,7 +41231,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="78" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:62">
       <c r="A78" s="18"/>
       <c r="B78" s="11" t="s">
         <v>170</v>
@@ -41395,7 +41417,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="79" spans="1:62" ht="45" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:62" ht="45">
       <c r="A79" s="16" t="s">
         <v>1099</v>
       </c>
@@ -41583,7 +41605,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="80" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:62" ht="30">
       <c r="A80" s="17"/>
       <c r="B80" s="7" t="s">
         <v>102</v>
@@ -41769,7 +41791,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="81" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:62">
       <c r="A81" s="17"/>
       <c r="B81" s="9" t="s">
         <v>111</v>
@@ -41955,7 +41977,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="82" spans="1:62" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:62">
       <c r="A82" s="18"/>
       <c r="B82" s="11" t="s">
         <v>170</v>
@@ -42141,7 +42163,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="83" spans="1:62" ht="135" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:62" ht="135">
       <c r="A83" s="16" t="s">
         <v>1108</v>
       </c>
@@ -42329,7 +42351,7 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="84" spans="1:62" ht="120" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:62" ht="120">
       <c r="A84" s="17"/>
       <c r="B84" s="7" t="s">
         <v>102</v>
@@ -42515,7 +42537,7 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="85" spans="1:62" ht="120" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:62" ht="120">
       <c r="A85" s="17"/>
       <c r="B85" s="9" t="s">
         <v>111</v>
@@ -42701,7 +42723,7 @@
         <v>1257</v>
       </c>
     </row>
-    <row r="86" spans="1:62" ht="195" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:62" ht="195">
       <c r="A86" s="18"/>
       <c r="B86" s="11" t="s">
         <v>170</v>
@@ -42889,6 +42911,14 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A83:A86"/>
+    <mergeCell ref="A39:A42"/>
+    <mergeCell ref="A15:A18"/>
+    <mergeCell ref="A59:A62"/>
+    <mergeCell ref="A35:A38"/>
+    <mergeCell ref="A51:A54"/>
+    <mergeCell ref="A79:A82"/>
+    <mergeCell ref="A75:A78"/>
     <mergeCell ref="A3:A6"/>
     <mergeCell ref="A55:A58"/>
     <mergeCell ref="A71:A74"/>
@@ -42902,17 +42932,9 @@
     <mergeCell ref="A67:A70"/>
     <mergeCell ref="A11:A14"/>
     <mergeCell ref="A7:A10"/>
-    <mergeCell ref="A83:A86"/>
-    <mergeCell ref="A39:A42"/>
-    <mergeCell ref="A15:A18"/>
-    <mergeCell ref="A59:A62"/>
-    <mergeCell ref="A35:A38"/>
-    <mergeCell ref="A51:A54"/>
-    <mergeCell ref="A79:A82"/>
-    <mergeCell ref="A75:A78"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
+  <pageMargins left="0.2" right="0" top="0.2" bottom="0.2" header="0" footer="0"/>
+  <pageSetup paperSize="9" scale="33" fitToWidth="6" fitToHeight="2" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>